--- a/templates/BOMBA_Roster_Template.xlsx
+++ b/templates/BOMBA_Roster_Template.xlsx
@@ -82,10 +82,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
-    <t xml:space="preserve">BOMBA Lineup Helper — Team Roster Template</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill in this file once per team, save it, then import it in the app (Roster ▸ Import from Excel).</t>
+    <t xml:space="preserve">CoachAssist — Team Roster Template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill in this file once per team, save it, then import it in CoachAssist (Roster ▸ Import from Excel).</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill it in</t>
